--- a/ig/feature-good-practices-interop/StructureDefinition-AS-HealthcareService-HealthCareActivity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-AS-HealthcareService-HealthCareActivity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:30:13+00:00</t>
+    <t>2023-04-04T08:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
